--- a/artfynd/A 5167-2020 artfynd.xlsx
+++ b/artfynd/A 5167-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117614074</v>
+        <v>117613934</v>
       </c>
       <c r="B2" t="n">
-        <v>57287</v>
+        <v>100070</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sågmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626699</v>
+        <v>626717</v>
       </c>
       <c r="R2" t="n">
-        <v>7217680</v>
+        <v>7217556</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117613934</v>
+        <v>117614074</v>
       </c>
       <c r="B3" t="n">
-        <v>100070</v>
+        <v>57287</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1365</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sågmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626717</v>
+        <v>626699</v>
       </c>
       <c r="R3" t="n">
-        <v>7217556</v>
+        <v>7217680</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117613932</v>
+        <v>117613931</v>
       </c>
       <c r="B4" t="n">
-        <v>100070</v>
+        <v>56491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +916,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1365</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sågmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626760</v>
+        <v>626725</v>
       </c>
       <c r="R4" t="n">
-        <v>7217566</v>
+        <v>7217597</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117613931</v>
+        <v>117613933</v>
       </c>
       <c r="B5" t="n">
-        <v>56491</v>
+        <v>79597</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,47 +1037,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sågmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626725</v>
+        <v>626749</v>
       </c>
       <c r="R5" t="n">
-        <v>7217597</v>
+        <v>7217563</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117613933</v>
+        <v>117613932</v>
       </c>
       <c r="B6" t="n">
-        <v>79597</v>
+        <v>100070</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,21 +1153,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>1365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626749</v>
+        <v>626760</v>
       </c>
       <c r="R6" t="n">
-        <v>7217563</v>
+        <v>7217566</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 5167-2020 artfynd.xlsx
+++ b/artfynd/A 5167-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117613934</v>
+        <v>117613931</v>
       </c>
       <c r="B2" t="n">
-        <v>100070</v>
+        <v>56492</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1365</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sågmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626717</v>
+        <v>626725</v>
       </c>
       <c r="R2" t="n">
-        <v>7217556</v>
+        <v>7217597</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117614074</v>
+        <v>117613933</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>79599</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +808,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sågmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626699</v>
+        <v>626749</v>
       </c>
       <c r="R3" t="n">
-        <v>7217680</v>
+        <v>7217563</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117613931</v>
+        <v>117613932</v>
       </c>
       <c r="B4" t="n">
-        <v>56491</v>
+        <v>100072</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,47 +920,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sågmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626725</v>
+        <v>626760</v>
       </c>
       <c r="R4" t="n">
-        <v>7217597</v>
+        <v>7217566</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117613933</v>
+        <v>117614074</v>
       </c>
       <c r="B5" t="n">
-        <v>79597</v>
+        <v>57288</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,38 +1032,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sågmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626749</v>
+        <v>626699</v>
       </c>
       <c r="R5" t="n">
-        <v>7217563</v>
+        <v>7217680</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117613932</v>
+        <v>117613934</v>
       </c>
       <c r="B6" t="n">
-        <v>100070</v>
+        <v>100072</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626760</v>
+        <v>626717</v>
       </c>
       <c r="R6" t="n">
-        <v>7217566</v>
+        <v>7217556</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 5167-2020 artfynd.xlsx
+++ b/artfynd/A 5167-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1247,6 +1247,117 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120472130</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100167</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sågmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>626737</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7217555</v>
+      </c>
+      <c r="S7" t="n">
+        <v>68</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>AC-Sto-0199</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
